--- a/data/raw/GLNPO 2024 Spring/Superior/D100/SU 01M D100 Spring 2024 24GS00I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Superior/D100/SU 01M D100 Spring 2024 24GS00I13 Zoop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GL Lab User\Desktop\GLNPO Sample Files\2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Superior\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D1FEDB-CAF8-4C33-8840-1E8E08B08BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6FA68F-8E42-415A-9C7D-E97CF506217E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{14AE481A-1B3A-4D41-A263-122B60039DD8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{14AE481A-1B3A-4D41-A263-122B60039DD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$160</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="959" r:id="rId2"/>
+    <pivotCache cacheId="44" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -398,24 +398,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3547,7 +3546,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56AC15B3-4596-4517-A5EB-111391831817}" name="PivotTable2" cacheId="959" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56AC15B3-4596-4517-A5EB-111391831817}" name="PivotTable2" cacheId="44" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U1:Z11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -3973,18 +3972,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86C76E09-5C6C-4567-B38D-2BE7ACE9CB16}">
   <dimension ref="A1:Z160"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="11" max="11" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4046,7 +4045,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -4117,7 +4116,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -4172,21 +4171,20 @@
       <c r="U3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="V3" s="4">
-        <v>20</v>
-      </c>
-      <c r="W3" s="4">
-        <v>19</v>
-      </c>
-      <c r="X3" s="4">
+      <c r="V3">
+        <v>20</v>
+      </c>
+      <c r="W3">
+        <v>19</v>
+      </c>
+      <c r="X3">
         <v>36</v>
       </c>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4">
+      <c r="Z3">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -4241,19 +4239,17 @@
       <c r="U4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="V4" s="4">
+      <c r="V4">
         <v>58</v>
       </c>
-      <c r="W4" s="4">
+      <c r="W4">
         <v>46</v>
       </c>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4">
+      <c r="Z4">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4308,21 +4304,20 @@
       <c r="U5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V5" s="4">
+      <c r="V5">
         <v>15</v>
       </c>
-      <c r="W5" s="4">
+      <c r="W5">
         <v>6</v>
       </c>
-      <c r="X5" s="4">
+      <c r="X5">
         <v>8</v>
       </c>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4">
+      <c r="Z5">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -4377,21 +4372,20 @@
       <c r="U6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="V6" s="4">
+      <c r="V6">
         <v>0</v>
       </c>
-      <c r="W6" s="4">
+      <c r="W6">
         <v>0</v>
       </c>
-      <c r="X6" s="4">
+      <c r="X6">
         <v>2</v>
       </c>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4">
+      <c r="Z6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4446,19 +4440,17 @@
       <c r="U7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V7">
         <v>68</v>
       </c>
-      <c r="W7" s="4">
+      <c r="W7">
         <v>68</v>
       </c>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4">
+      <c r="Z7">
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -4513,21 +4505,20 @@
       <c r="U8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V8">
         <v>11</v>
       </c>
-      <c r="W8" s="4">
+      <c r="W8">
         <v>5</v>
       </c>
-      <c r="X8" s="4">
+      <c r="X8">
         <v>10</v>
       </c>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4">
+      <c r="Z8">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4582,23 +4573,23 @@
       <c r="U9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9">
         <v>0</v>
       </c>
-      <c r="W9" s="4">
-        <v>1</v>
-      </c>
-      <c r="X9" s="4">
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
         <v>0</v>
       </c>
-      <c r="Y9" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="4">
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4653,21 +4644,20 @@
       <c r="U10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V10" s="4">
+      <c r="V10">
         <v>7</v>
       </c>
-      <c r="W10" s="4">
+      <c r="W10">
         <v>5</v>
       </c>
-      <c r="X10" s="4">
+      <c r="X10">
         <v>8</v>
       </c>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4722,23 +4712,23 @@
       <c r="U11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="V11" s="4">
+      <c r="V11">
         <v>179</v>
       </c>
-      <c r="W11" s="4">
+      <c r="W11">
         <v>150</v>
       </c>
-      <c r="X11" s="4">
+      <c r="X11">
         <v>64</v>
       </c>
-      <c r="Y11" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="4">
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
         <v>394</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -4791,7 +4781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4843,17 +4833,17 @@
       <c r="Q13">
         <v>1</v>
       </c>
-      <c r="U13" s="6" t="s">
+      <c r="U13" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="V13" s="7" t="s">
+      <c r="V13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="W13" s="8">
+      <c r="W13" s="6">
         <v>0.996</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -4906,14 +4896,14 @@
         <v>1</v>
       </c>
       <c r="U14" s="9"/>
-      <c r="V14" s="7" t="s">
+      <c r="V14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="W14" s="8">
+      <c r="W14" s="6">
         <v>0.996</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4965,17 +4955,17 @@
       <c r="Q15">
         <v>1</v>
       </c>
-      <c r="U15" s="6" t="s">
+      <c r="U15" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="V15" s="7" t="s">
+      <c r="V15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="W15" s="8">
+      <c r="W15" s="6">
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -5028,14 +5018,14 @@
         <v>1</v>
       </c>
       <c r="U16" s="9"/>
-      <c r="V16" s="7" t="s">
+      <c r="V16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="W16" s="8">
+      <c r="W16" s="6">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -5087,15 +5077,15 @@
       <c r="Q17">
         <v>1</v>
       </c>
-      <c r="U17" s="10" t="s">
+      <c r="U17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="V17" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="W17" s="12"/>
-    </row>
-    <row r="18" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W17" s="11"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -5147,15 +5137,15 @@
       <c r="Q18">
         <v>1</v>
       </c>
-      <c r="U18" s="10" t="s">
+      <c r="U18" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="V18" s="11" t="s">
+      <c r="V18" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="W18" s="12"/>
-    </row>
-    <row r="19" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W18" s="11"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -5207,13 +5197,13 @@
       <c r="Q19">
         <v>1</v>
       </c>
-      <c r="U19" s="7" t="s">
+      <c r="U19" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="V19" s="11"/>
-      <c r="W19" s="12"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V19" s="10"/>
+      <c r="W19" s="11"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -5266,7 +5256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -5319,7 +5309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -5372,7 +5362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -5425,7 +5415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -5478,7 +5468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -5531,7 +5521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -5584,7 +5574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -5637,7 +5627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -5693,7 +5683,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -5746,7 +5736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -5799,7 +5789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -5852,7 +5842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -5905,7 +5895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -5958,7 +5948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -6011,7 +6001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -6064,7 +6054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -6117,7 +6107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -6170,7 +6160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -6223,7 +6213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -6276,7 +6266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -6329,7 +6319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -6382,7 +6372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -6435,7 +6425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -6488,7 +6478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -6541,7 +6531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -6594,7 +6584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -6647,7 +6637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -6700,7 +6690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -6753,7 +6743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -6806,7 +6796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -6859,7 +6849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -6912,7 +6902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -6965,7 +6955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -7018,7 +7008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -7071,7 +7061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -7124,7 +7114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -7177,7 +7167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -7230,7 +7220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -7283,7 +7273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -7336,7 +7326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -7389,7 +7379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -7442,7 +7432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -7495,7 +7485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -7548,7 +7538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -7601,7 +7591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -7654,7 +7644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -7707,7 +7697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -7760,7 +7750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -7813,7 +7803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -7866,7 +7856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -7919,7 +7909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -7972,7 +7962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -8025,7 +8015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -8078,7 +8068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -8131,7 +8121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -8184,7 +8174,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -8237,7 +8227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -8290,7 +8280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -8343,7 +8333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -8396,7 +8386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -8449,7 +8439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -8502,7 +8492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -8555,7 +8545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -8608,7 +8598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -8661,7 +8651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -8714,7 +8704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -8767,7 +8757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -8820,7 +8810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -8873,7 +8863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -8926,7 +8916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -8979,7 +8969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -9032,7 +9022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -9085,7 +9075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -9138,7 +9128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -9191,7 +9181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -9244,7 +9234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -9297,7 +9287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -9350,7 +9340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -9403,7 +9393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -9456,7 +9446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -9509,7 +9499,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -9562,7 +9552,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -9615,7 +9605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -9668,7 +9658,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -9721,7 +9711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -9774,7 +9764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -9827,7 +9817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -9880,7 +9870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -9933,7 +9923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -9986,7 +9976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -10039,7 +10029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -10092,7 +10082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -10148,7 +10138,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -10201,7 +10191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -10254,7 +10244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -10307,7 +10297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -10360,7 +10350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -10413,7 +10403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -10466,7 +10456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -10519,7 +10509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -10572,7 +10562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -10625,7 +10615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -10678,7 +10668,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -10731,7 +10721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -10784,7 +10774,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -10837,7 +10827,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -10890,7 +10880,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -10943,7 +10933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -10996,7 +10986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -11049,7 +11039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -11102,7 +11092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -11155,7 +11145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -11208,7 +11198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -11261,7 +11251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -11314,7 +11304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -11367,7 +11357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -11420,7 +11410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -11473,7 +11463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -11526,7 +11516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -11579,7 +11569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -11632,7 +11622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -11685,7 +11675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -11738,7 +11728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -11791,7 +11781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -11844,7 +11834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -11897,7 +11887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -11944,13 +11934,13 @@
         <v>0.93100000000000005</v>
       </c>
       <c r="P146" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q146">
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -12003,7 +11993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -12056,7 +12046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -12109,7 +12099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -12162,7 +12152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -12215,7 +12205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -12268,7 +12258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -12321,7 +12311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -12374,7 +12364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -12427,7 +12417,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -12480,215 +12470,215 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D157" s="5">
-        <v>-1</v>
-      </c>
-      <c r="E157" s="5" t="s">
+    <row r="157" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D157" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E157" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F157" s="5" t="s">
+      <c r="F157" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G157" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H157" s="5" t="s">
+      <c r="G157" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H157" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I157" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J157" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K157" s="5" t="s">
+      <c r="I157" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J157" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K157" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L157" s="5" t="s">
+      <c r="L157" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M157" s="5" t="s">
+      <c r="M157" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N157" s="5" t="s">
+      <c r="N157" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O157" s="5" t="s">
+      <c r="O157" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P157" s="5" t="s">
+      <c r="P157" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q157" s="5">
+      <c r="Q157" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D158" s="5">
-        <v>-1</v>
-      </c>
-      <c r="E158" s="5" t="s">
+    <row r="158" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D158" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E158" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F158" s="5" t="s">
+      <c r="F158" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G158" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H158" s="5" t="s">
+      <c r="G158" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H158" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I158" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J158" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K158" s="5" t="s">
+      <c r="I158" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J158" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K158" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L158" s="5" t="s">
+      <c r="L158" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M158" s="5" t="s">
+      <c r="M158" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N158" s="5" t="s">
+      <c r="N158" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O158" s="5" t="s">
+      <c r="O158" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P158" s="5" t="s">
+      <c r="P158" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q158" s="5">
+      <c r="Q158" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D159" s="5">
-        <v>-1</v>
-      </c>
-      <c r="E159" s="5" t="s">
+    <row r="159" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D159" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E159" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F159" s="5" t="s">
+      <c r="F159" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G159" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H159" s="5" t="s">
+      <c r="G159" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H159" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I159" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J159" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K159" s="5" t="s">
+      <c r="I159" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J159" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K159" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L159" s="5" t="s">
+      <c r="L159" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="M159" s="5" t="s">
+      <c r="M159" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N159" s="5" t="s">
+      <c r="N159" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O159" s="5" t="s">
+      <c r="O159" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P159" s="5" t="s">
+      <c r="P159" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q159" s="5">
+      <c r="Q159" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D160" s="5">
-        <v>-1</v>
-      </c>
-      <c r="E160" s="5" t="s">
+    <row r="160" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D160" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E160" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F160" s="5" t="s">
+      <c r="F160" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G160" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H160" s="5" t="s">
+      <c r="G160" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H160" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I160" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J160" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K160" s="5" t="s">
+      <c r="I160" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J160" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K160" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L160" s="5" t="s">
+      <c r="L160" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="M160" s="5" t="s">
+      <c r="M160" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N160" s="5" t="s">
+      <c r="N160" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O160" s="5" t="s">
+      <c r="O160" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P160" s="5" t="s">
+      <c r="P160" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q160" s="5">
+      <c r="Q160" s="4">
         <v>0</v>
       </c>
     </row>
